--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/audit_findings.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/audit_findings.xlsx
@@ -495,12 +495,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-11-16</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
@@ -625,17 +625,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
     </row>
@@ -652,17 +652,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-18</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-03-15</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-01-17</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-07-13</t>
         </is>
       </c>
     </row>
@@ -841,17 +841,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-08-05</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-10-23</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-04-12</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-04-22</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-11</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-12-21</t>
         </is>
       </c>
     </row>
@@ -1052,22 +1052,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
     </row>
@@ -1079,22 +1079,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1133,22 +1133,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-22</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
     </row>
@@ -1192,17 +1192,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1241,22 +1241,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-09-19</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-04-23</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-12-22</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-02-16</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-06-20</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-01-06</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-06-26</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-11-16</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>External</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2025-08-25</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-10-07</t>
         </is>
       </c>
     </row>
